--- a/docs/Decodifiche/153_dmnm_dec_conf_causa_morte.xlsx
+++ b/docs/Decodifiche/153_dmnm_dec_conf_causa_morte.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
   <si>
     <t>ID</t>
   </si>
@@ -35,7 +35,7 @@
     <t>(SI)</t>
   </si>
   <si>
-    <t>2025-12-02 20:23:15.0</t>
+    <t>2025-12-04 11:48:12.0</t>
   </si>
   <si>
     <t>9999-12-31 00:00:00.0</t>
@@ -45,9 +45,6 @@
   </si>
   <si>
     <t>(NO)</t>
-  </si>
-  <si>
-    <t>2025-12-02 20:23:16.0</t>
   </si>
 </sst>
 </file>
@@ -158,7 +155,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>8</v>
